--- a/Result/profitability/5465.xlsx
+++ b/Result/profitability/5465.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2875</v>
+        <v>0.31625</v>
       </c>
       <c r="N2" t="n">
-        <v>13.8025</v>
+        <v>13.84875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.11125</v>
+        <v>0.1225</v>
       </c>
       <c r="N3" t="n">
-        <v>12.1125</v>
+        <v>12.5775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02249999999999999</v>
+        <v>0.0175</v>
       </c>
       <c r="N4" t="n">
-        <v>11.8675</v>
+        <v>12.39625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.15375</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>10.98</v>
+        <v>12.05125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.21125</v>
+        <v>-0.225</v>
       </c>
       <c r="N6" t="n">
-        <v>10.95625</v>
+        <v>11.8175</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.33875</v>
+        <v>-0.255</v>
       </c>
       <c r="N7" t="n">
-        <v>11.0225</v>
+        <v>11.61375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.33375</v>
+        <v>-0.30875</v>
       </c>
       <c r="N8" t="n">
-        <v>11.6075</v>
+        <v>12.19125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.05</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.07500000000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="N13" t="n">
         <v>18.53375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5465</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>937</v>
+      </c>
+      <c r="D75" t="n">
+        <v>757</v>
+      </c>
+      <c r="E75" t="n">
+        <v>180</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="G75" t="n">
+        <v>90</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.62%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>100</v>
+      </c>
+      <c r="K75" t="n">
+        <v>86</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.0625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.670000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3211829436038516</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.8054511278195489</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
